--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3de78c61e5c57f5d4730eb96c8d1978890f72b2503adec0187be5b33fd74fb37</t>
+          <t>513a8941089c265ec784294e455858f7e324d823b58e52fe43d82fb10ff94182</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-02 22:43:55</t>
+          <t>2026-07-03 18:32:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>host@citi.com</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>QuizTok Host</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2fca8f65fe499736129e771cf13e1a4390b0b2d2ef8bb76383bb22ccb1d02fc6</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-07-03 18:32:09</t>
         </is>
       </c>
     </row>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>admin@citi.com</t>
+          <t>admin@abc.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>host@citi.com</t>
+          <t>host@abc.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
